--- a/Assets/Excel/TalentData.xlsx
+++ b/Assets/Excel/TalentData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15870" windowHeight="9825"/>
+    <workbookView windowWidth="23535" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="40">
   <si>
     <t>id</t>
   </si>
@@ -46,6 +46,9 @@
     <t>info</t>
   </si>
   <si>
+    <t>kuangResName</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -73,21 +76,45 @@
     <t>信息描述</t>
   </si>
   <si>
+    <t>底框资源</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
     <t>攻击力\n+10</t>
   </si>
   <si>
+    <t>绿框</t>
+  </si>
+  <si>
+    <t>生命值</t>
+  </si>
+  <si>
     <t>健康值\n+50</t>
   </si>
   <si>
+    <t>储物袋扩容</t>
+  </si>
+  <si>
     <t>储物袋容量\n+20</t>
   </si>
   <si>
+    <t>紫框</t>
+  </si>
+  <si>
+    <t>速度</t>
+  </si>
+  <si>
     <t>0.07f</t>
   </si>
   <si>
     <t>移动速度\n+百分之7</t>
   </si>
   <si>
+    <t>攻击范围</t>
+  </si>
+  <si>
     <t>0.25f</t>
   </si>
   <si>
@@ -97,6 +124,12 @@
     <t>储物袋容量\n+10</t>
   </si>
   <si>
+    <t>橙框</t>
+  </si>
+  <si>
+    <t>储物袋吸纳</t>
+  </si>
+  <si>
     <t>0.1f</t>
   </si>
   <si>
@@ -104,6 +137,9 @@
   </si>
   <si>
     <t>移动速度\n+10%</t>
+  </si>
+  <si>
+    <t>攻击恢复</t>
   </si>
   <si>
     <t>击败灵植或灵石\n+20</t>
@@ -1046,16 +1082,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E83"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="12.375" customWidth="1"/>
     <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1071,47 +1108,56 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="1">
-        <v>2</v>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1120,15 +1166,18 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="1">
-        <v>2</v>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1137,15 +1186,18 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="1">
-        <v>2</v>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1154,15 +1206,18 @@
         <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>2</v>
+      <c r="B7" t="s">
+        <v>21</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -1171,15 +1226,18 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8">
-        <v>2</v>
+      <c r="B8" t="s">
+        <v>16</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1188,15 +1246,18 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9">
-        <v>2</v>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1205,15 +1266,18 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10">
-        <v>2</v>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -1222,15 +1286,18 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11">
-        <v>2</v>
+      <c r="B11" t="s">
+        <v>16</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1239,15 +1306,18 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12">
-        <v>2</v>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1256,32 +1326,38 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13">
-        <v>2</v>
+      <c r="B13" t="s">
+        <v>24</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14">
-        <v>2</v>
+      <c r="B14" t="s">
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1290,15 +1366,18 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15">
-        <v>2</v>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1307,15 +1386,18 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16">
-        <v>2</v>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -1324,15 +1406,18 @@
         <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17">
-        <v>2</v>
+      <c r="B17" t="s">
+        <v>16</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1341,15 +1426,18 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18">
-        <v>2</v>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1358,15 +1446,18 @@
         <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19">
-        <v>2</v>
+      <c r="B19" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1375,32 +1466,38 @@
         <v>50</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20">
-        <v>2</v>
+      <c r="B20" t="s">
+        <v>27</v>
       </c>
       <c r="C20">
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21">
-        <v>2</v>
+      <c r="B21" t="s">
+        <v>16</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1409,15 +1506,18 @@
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22">
-        <v>2</v>
+      <c r="B22" t="s">
+        <v>16</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1426,15 +1526,18 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23">
-        <v>2</v>
+      <c r="B23" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -1443,15 +1546,18 @@
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24">
-        <v>2</v>
+      <c r="B24" t="s">
+        <v>16</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1460,15 +1566,18 @@
         <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25">
-        <v>2</v>
+      <c r="B25" t="s">
+        <v>16</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1477,15 +1586,18 @@
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26">
-        <v>2</v>
+      <c r="B26" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -1494,15 +1606,18 @@
         <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27">
-        <v>2</v>
+      <c r="B27" t="s">
+        <v>21</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -1511,15 +1626,18 @@
         <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28">
-        <v>2</v>
+      <c r="B28" t="s">
+        <v>16</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1528,15 +1646,18 @@
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29">
-        <v>2</v>
+      <c r="B29" t="s">
+        <v>16</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1545,15 +1666,18 @@
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30">
-        <v>2</v>
+      <c r="B30" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -1562,15 +1686,18 @@
         <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31">
-        <v>2</v>
+      <c r="B31" t="s">
+        <v>16</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1579,15 +1706,18 @@
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32">
-        <v>2</v>
+      <c r="B32" t="s">
+        <v>16</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1596,15 +1726,18 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33">
-        <v>2</v>
+      <c r="B33" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1613,32 +1746,38 @@
         <v>50</v>
       </c>
       <c r="E33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34">
-        <v>2</v>
+      <c r="B34" t="s">
+        <v>32</v>
       </c>
       <c r="C34">
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>34</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35">
-        <v>2</v>
+      <c r="B35" t="s">
+        <v>16</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1647,15 +1786,18 @@
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36">
-        <v>2</v>
+      <c r="B36" t="s">
+        <v>16</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1664,15 +1806,18 @@
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37">
-        <v>2</v>
+      <c r="B37" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1681,15 +1826,18 @@
         <v>50</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38">
-        <v>2</v>
+      <c r="B38" t="s">
+        <v>16</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1698,15 +1846,18 @@
         <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39">
-        <v>2</v>
+      <c r="B39" t="s">
+        <v>16</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1715,15 +1866,18 @@
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40">
-        <v>2</v>
+      <c r="B40" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -1732,32 +1886,38 @@
         <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41">
-        <v>2</v>
+      <c r="B41" t="s">
+        <v>24</v>
       </c>
       <c r="C41">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42">
-        <v>2</v>
+      <c r="B42" t="s">
+        <v>16</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -1766,15 +1926,18 @@
         <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43">
-        <v>2</v>
+      <c r="B43" t="s">
+        <v>16</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1783,15 +1946,18 @@
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44">
-        <v>2</v>
+      <c r="B44" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1800,15 +1966,18 @@
         <v>50</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45">
-        <v>2</v>
+      <c r="B45" t="s">
+        <v>16</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1817,15 +1986,18 @@
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46">
-        <v>2</v>
+      <c r="B46" t="s">
+        <v>16</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1834,15 +2006,18 @@
         <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47">
-        <v>2</v>
+      <c r="B47" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -1851,15 +2026,18 @@
         <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48">
-        <v>2</v>
+      <c r="B48" t="s">
+        <v>16</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1868,15 +2046,18 @@
         <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49">
-        <v>2</v>
+      <c r="B49" t="s">
+        <v>16</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1885,15 +2066,18 @@
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50">
-        <v>2</v>
+      <c r="B50" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -1902,15 +2086,18 @@
         <v>50</v>
       </c>
       <c r="E50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51">
-        <v>2</v>
+      <c r="B51" t="s">
+        <v>36</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -1919,15 +2106,18 @@
         <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>37</v>
+      </c>
+      <c r="F51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52">
-        <v>2</v>
+      <c r="B52" t="s">
+        <v>16</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1936,15 +2126,18 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53">
-        <v>2</v>
+      <c r="B53" t="s">
+        <v>16</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1953,15 +2146,18 @@
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54">
-        <v>2</v>
+      <c r="B54" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -1970,15 +2166,18 @@
         <v>50</v>
       </c>
       <c r="E54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55">
-        <v>2</v>
+      <c r="B55" t="s">
+        <v>16</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1987,15 +2186,18 @@
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56">
-        <v>2</v>
+      <c r="B56" t="s">
+        <v>16</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2004,15 +2206,18 @@
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57">
-        <v>2</v>
+      <c r="B57" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -2021,15 +2226,18 @@
         <v>50</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58">
-        <v>2</v>
+      <c r="B58" t="s">
+        <v>16</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -2038,15 +2246,18 @@
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59">
-        <v>2</v>
+      <c r="B59" t="s">
+        <v>16</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -2055,15 +2266,18 @@
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60">
-        <v>2</v>
+      <c r="B60" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -2072,32 +2286,38 @@
         <v>50</v>
       </c>
       <c r="E60" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61">
-        <v>2</v>
+      <c r="B61" t="s">
+        <v>24</v>
       </c>
       <c r="C61">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E61" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>39</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62">
-        <v>2</v>
+      <c r="B62" t="s">
+        <v>16</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -2106,15 +2326,18 @@
         <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63">
-        <v>2</v>
+      <c r="B63" t="s">
+        <v>16</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -2123,15 +2346,18 @@
         <v>10</v>
       </c>
       <c r="E63" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64">
-        <v>2</v>
+      <c r="B64" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -2140,15 +2366,18 @@
         <v>50</v>
       </c>
       <c r="E64" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65">
-        <v>2</v>
+      <c r="B65" t="s">
+        <v>16</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -2157,15 +2386,18 @@
         <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66">
-        <v>2</v>
+      <c r="B66" t="s">
+        <v>16</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2174,15 +2406,18 @@
         <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67">
-        <v>2</v>
+      <c r="B67" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -2191,15 +2426,18 @@
         <v>50</v>
       </c>
       <c r="E67" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68">
-        <v>2</v>
+      <c r="B68" t="s">
+        <v>16</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -2208,15 +2446,18 @@
         <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69">
-        <v>2</v>
+      <c r="B69" t="s">
+        <v>16</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -2225,15 +2466,18 @@
         <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70">
-        <v>2</v>
+      <c r="B70" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -2242,15 +2486,18 @@
         <v>50</v>
       </c>
       <c r="E70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71">
-        <v>2</v>
+      <c r="B71" t="s">
+        <v>21</v>
       </c>
       <c r="C71">
         <v>3</v>
@@ -2259,15 +2506,18 @@
         <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>30</v>
+      </c>
+      <c r="F71" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72">
-        <v>2</v>
+      <c r="B72" t="s">
+        <v>16</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -2276,15 +2526,18 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73">
-        <v>2</v>
+      <c r="B73" t="s">
+        <v>16</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -2293,15 +2546,18 @@
         <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74">
         <v>71</v>
       </c>
-      <c r="B74">
-        <v>2</v>
+      <c r="B74" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C74">
         <v>2</v>
@@ -2310,15 +2566,18 @@
         <v>50</v>
       </c>
       <c r="E74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75">
         <v>72</v>
       </c>
-      <c r="B75">
-        <v>2</v>
+      <c r="B75" t="s">
+        <v>16</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -2327,15 +2586,18 @@
         <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76">
         <v>73</v>
       </c>
-      <c r="B76">
-        <v>2</v>
+      <c r="B76" t="s">
+        <v>16</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -2344,15 +2606,18 @@
         <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77">
         <v>74</v>
       </c>
-      <c r="B77">
-        <v>2</v>
+      <c r="B77" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C77">
         <v>2</v>
@@ -2361,15 +2626,18 @@
         <v>50</v>
       </c>
       <c r="E77" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78">
         <v>75</v>
       </c>
-      <c r="B78">
-        <v>2</v>
+      <c r="B78" t="s">
+        <v>16</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -2378,15 +2646,18 @@
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79">
         <v>76</v>
       </c>
-      <c r="B79">
-        <v>2</v>
+      <c r="B79" t="s">
+        <v>16</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -2395,15 +2666,18 @@
         <v>10</v>
       </c>
       <c r="E79" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80">
         <v>77</v>
       </c>
-      <c r="B80">
-        <v>2</v>
+      <c r="B80" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -2412,32 +2686,38 @@
         <v>50</v>
       </c>
       <c r="E80" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81">
         <v>78</v>
       </c>
-      <c r="B81">
-        <v>2</v>
+      <c r="B81" t="s">
+        <v>27</v>
       </c>
       <c r="C81">
         <v>5</v>
       </c>
       <c r="D81" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E81" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>29</v>
+      </c>
+      <c r="F81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82">
         <v>79</v>
       </c>
-      <c r="B82">
-        <v>2</v>
+      <c r="B82" t="s">
+        <v>16</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -2446,15 +2726,18 @@
         <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83">
         <v>80</v>
       </c>
-      <c r="B83">
-        <v>2</v>
+      <c r="B83" t="s">
+        <v>16</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -2463,7 +2746,10 @@
         <v>10</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/TalentData.xlsx
+++ b/Assets/Excel/TalentData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23535" windowHeight="10260"/>
+    <workbookView windowWidth="19140" windowHeight="10395"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
     <t>0.07f</t>
   </si>
   <si>
-    <t>移动速度\n+百分之7</t>
+    <t>移动速度\n+7%</t>
   </si>
   <si>
     <t>攻击范围</t>
@@ -118,7 +118,7 @@
     <t>0.25f</t>
   </si>
   <si>
-    <t>武器尺寸\n+百分之25</t>
+    <t>武器尺寸\n+25%</t>
   </si>
   <si>
     <t>储物袋容量\n+10</t>
@@ -142,7 +142,7 @@
     <t>攻击恢复</t>
   </si>
   <si>
-    <t>击败灵植或灵石\n+20</t>
+    <t>击败灵植或矿石\n+20</t>
   </si>
   <si>
     <t>0.08f</t>
